--- a/Piaui/2026/ResultadosTRI_3EM_MT/Simulado_I/ResumoThetaIC_3EM_MT_S1.xlsx
+++ b/Piaui/2026/ResultadosTRI_3EM_MT/Simulado_I/ResumoThetaIC_3EM_MT_S1.xlsx
@@ -395,22 +395,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>280.38</v>
+        <v>289.789</v>
       </c>
       <c r="C2" t="n">
-        <v>279.047</v>
+        <v>288.314</v>
       </c>
       <c r="D2" t="n">
-        <v>281.712</v>
+        <v>291.265</v>
       </c>
       <c r="E2" t="n">
-        <v>71.293</v>
+        <v>78.211</v>
       </c>
       <c r="F2" t="n">
-        <v>69.151</v>
+        <v>75.527</v>
       </c>
       <c r="G2" t="n">
-        <v>73.435</v>
+        <v>80.895</v>
       </c>
     </row>
     <row r="3">
@@ -418,22 +418,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>0.608</v>
+        <v>0.796</v>
       </c>
       <c r="C3" t="n">
-        <v>0.581</v>
+        <v>0.766</v>
       </c>
       <c r="D3" t="n">
-        <v>0.634</v>
+        <v>0.825</v>
       </c>
       <c r="E3" t="n">
-        <v>1.426</v>
+        <v>1.564</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4</v>
+        <v>1.534</v>
       </c>
       <c r="G3" t="n">
-        <v>1.451</v>
+        <v>1.594</v>
       </c>
     </row>
   </sheetData>

--- a/Piaui/2026/ResultadosTRI_3EM_MT/Simulado_I/ResumoThetaIC_3EM_MT_S1.xlsx
+++ b/Piaui/2026/ResultadosTRI_3EM_MT/Simulado_I/ResumoThetaIC_3EM_MT_S1.xlsx
@@ -395,22 +395,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>289.789</v>
+        <v>280.38</v>
       </c>
       <c r="C2" t="n">
-        <v>288.314</v>
+        <v>279.047</v>
       </c>
       <c r="D2" t="n">
-        <v>291.265</v>
+        <v>281.712</v>
       </c>
       <c r="E2" t="n">
-        <v>78.211</v>
+        <v>71.293</v>
       </c>
       <c r="F2" t="n">
-        <v>75.527</v>
+        <v>69.151</v>
       </c>
       <c r="G2" t="n">
-        <v>80.895</v>
+        <v>73.435</v>
       </c>
     </row>
     <row r="3">
@@ -418,22 +418,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>0.796</v>
+        <v>0.608</v>
       </c>
       <c r="C3" t="n">
-        <v>0.766</v>
+        <v>0.581</v>
       </c>
       <c r="D3" t="n">
-        <v>0.825</v>
+        <v>0.634</v>
       </c>
       <c r="E3" t="n">
-        <v>1.564</v>
+        <v>1.426</v>
       </c>
       <c r="F3" t="n">
-        <v>1.534</v>
+        <v>1.4</v>
       </c>
       <c r="G3" t="n">
-        <v>1.594</v>
+        <v>1.451</v>
       </c>
     </row>
   </sheetData>
